--- a/input/test_dataset/test_dataset.xlsx
+++ b/input/test_dataset/test_dataset.xlsx
@@ -421,7 +421,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ejincometaxpreperation.com</v>
+        <v>uidaiaadhardownload.com</v>
       </c>
     </row>
     <row r="6">
